--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,69 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>KEVIN HONAM</t>
   </si>
 </sst>
 </file>
@@ -773,7 +836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +866,167 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920111</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920120</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920130</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920312</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -88,18 +103,27 @@
     <t>QUERO</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -109,18 +133,27 @@
     <t>SERRANO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
   </si>
   <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>NATALIE</t>
   </si>
   <si>
@@ -130,13 +163,7 @@
     <t>EDWIN YAMIL</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>KEVIN HONAM</t>
+    <t>GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -654,16 +681,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>53.57</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -677,16 +707,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -700,16 +733,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -765,16 +801,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>53.57</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,16 +827,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>81.25</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,13 +853,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -836,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -868,16 +904,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920111</v>
+        <v>21330051920115</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -891,16 +927,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920120</v>
+        <v>21330051920133</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -914,22 +950,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920127</v>
+        <v>19330051920353</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -937,16 +973,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920130</v>
+        <v>21330051920111</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -955,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -966,10 +1002,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -983,16 +1019,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920115</v>
+        <v>21330051920114</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1006,24 +1042,93 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920312</v>
+        <v>21330051920120</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920334</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
         <v>9</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F11" t="s">
         <v>11</v>
       </c>
-      <c r="G8">
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>XOLIO</t>
@@ -88,9 +91,6 @@
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>CERON</t>
   </si>
   <si>
@@ -103,13 +103,13 @@
     <t>QUERO</t>
   </si>
   <si>
-    <t>MENDOZA</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>GARNICA</t>
   </si>
   <si>
-    <t>MONTIEL</t>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -118,9 +118,6 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
@@ -133,13 +130,13 @@
     <t>SERRANO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>DIEGO</t>
   </si>
   <si>
     <t>DIEGO DE JESUS</t>
   </si>
   <si>
-    <t>CESAR DANIEL</t>
+    <t>MELANY NARAYANA</t>
   </si>
   <si>
     <t>HERSON ELIAS</t>
@@ -148,9 +145,6 @@
     <t>KAREN ITZEL</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
@@ -161,9 +155,6 @@
   </si>
   <si>
     <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
   </si>
 </sst>
 </file>
@@ -872,7 +863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -904,16 +895,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920115</v>
+        <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -927,16 +918,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920133</v>
+        <v>21330051920115</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -950,22 +941,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920353</v>
+        <v>21330051920134</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -973,39 +964,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920111</v>
+        <v>19330051920353</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920112</v>
+        <v>21330051920111</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1025,10 +1016,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1048,10 +1039,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1071,10 +1062,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1094,10 +1085,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1106,29 +1097,6 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920334</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -79,82 +79,55 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>PALMA</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>MELANY NARAYANA</t>
-  </si>
-  <si>
     <t>HERSON ELIAS</t>
   </si>
   <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
+    <t>JOSE EMMANUEL</t>
   </si>
   <si>
     <t>NATALIE</t>
   </si>
   <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -792,16 +765,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>53.57</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -844,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>87.5</v>
+        <v>81.25</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -863,7 +836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,10 +874,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -918,22 +891,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920115</v>
+        <v>19330051920353</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -941,22 +914,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920134</v>
+        <v>19330051920247</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -964,39 +937,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920353</v>
+        <v>21330051920120</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920111</v>
+        <v>21330051920125</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1010,93 +983,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920114</v>
+        <v>19330051920251</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920120</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920127</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920130</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="59">
   <si>
     <t>Mat</t>
   </si>
@@ -76,58 +76,124 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>XOLIO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PALMA</t>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
     <t>HERSON ELIAS</t>
   </si>
   <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
     <t>VALERIA</t>
+  </si>
+  <si>
+    <t>EDUARDO ULISES</t>
   </si>
 </sst>
 </file>
@@ -836,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -868,7 +934,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920112</v>
+        <v>20330051920152</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -877,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -891,22 +957,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920353</v>
+        <v>21330051920133</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -914,22 +980,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920247</v>
+        <v>19330051920308</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -937,62 +1003,62 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920120</v>
+        <v>19330051920350</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920125</v>
+        <v>19330051920259</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920251</v>
+        <v>19330051920412</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1001,6 +1067,190 @@
         <v>12</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920120</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920321</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920334</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920353</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920251</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920403</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
